--- a/selenium_test_cases.xlsx
+++ b/selenium_test_cases.xlsx
@@ -5448,7 +5448,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-06-16 10:48:58</t>
+          <t>2026-06-16 12:51:00</t>
         </is>
       </c>
     </row>
@@ -5472,7 +5472,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>selenium_test_1781587135@example.com</t>
+          <t>selenium_test_1781594456@example.com</t>
         </is>
       </c>
     </row>

--- a/selenium_test_cases.xlsx
+++ b/selenium_test_cases.xlsx
@@ -5448,7 +5448,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-06-16 12:51:00</t>
+          <t>2026-06-16 13:07:56</t>
         </is>
       </c>
     </row>
@@ -5460,7 +5460,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>http://localhost/finalproject</t>
+          <t>https://karthiksites.byethost11.com</t>
         </is>
       </c>
     </row>
@@ -5472,7 +5472,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>selenium_test_1781594456@example.com</t>
+          <t>selenium_test_1781595471@example.com</t>
         </is>
       </c>
     </row>
